--- a/8月9月不缺料订单清单.xlsx
+++ b/8月9月不缺料订单清单.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,19 +514,19 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PSO2302251</t>
+          <t>MSO2500085</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4500549532</v>
+        <v>4500578342</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>SP8005/BNTMB9100BR</t>
+          <t>SP8360/5572U</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>282</v>
+        <v>5004</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -540,15 +540,15 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>BRAZIL</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45915</v>
+        <v>45930</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>P8005-L02-C1203</t>
+          <t>P8360-E01-M1207</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>9966.444</v>
+        <v>44745.768</v>
       </c>
       <c r="M2" t="n">
-        <v>72755.04119999999</v>
+        <v>81045.768</v>
       </c>
       <c r="N2" t="n">
         <v>-1</v>
@@ -579,19 +579,19 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PSO2302252</t>
+          <t>MSO2500101</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4500549532</v>
+        <v>4500576348</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>SP8005/BNTMB9100BRB</t>
+          <t>SP8515/2136U</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>216</v>
+        <v>10008</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -605,15 +605,15 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>BRAZIL</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>45915</v>
+        <v>45918</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>P8005-V02-C1203</t>
+          <t>P8515-E01-M1203</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>7949.448</v>
+        <v>131505.12</v>
       </c>
       <c r="M3" t="n">
-        <v>72755.04119999999</v>
+        <v>502532.2044</v>
       </c>
       <c r="N3" t="n">
         <v>-1</v>
@@ -644,23 +644,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PSO2500659</t>
+          <t>PSO2302251</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4500574195</v>
+        <v>4500549532</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>SP8341/D212SDE</t>
+          <t>SP8005/BNTMB9100BR</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1248</v>
+        <v>282</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -670,15 +670,15 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SAUDI ARABIA</t>
+          <t>BRAZIL</t>
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45853</v>
+        <v>45915</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>P8341-S02-C1201</t>
+          <t>P8005-L02-C1203</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -692,10 +692,10 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>7378.176</v>
+        <v>9966.444</v>
       </c>
       <c r="M4" t="n">
-        <v>53860.6848</v>
+        <v>72755.04119999999</v>
       </c>
       <c r="N4" t="n">
         <v>-1</v>
@@ -709,23 +709,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PSO2500737</t>
+          <t>PSO2302252</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4500575187</v>
+        <v>4500549532</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>SP8526/BNTHB300TUZ</t>
+          <t>SP8005/BNTMB9100BRB</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1002</v>
+        <v>216</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -735,15 +735,15 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CHILE</t>
+          <t>BRAZIL</t>
         </is>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45874</v>
+        <v>45915</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>P8526-V01-C1203</t>
+          <t>P8005-V02-C1203</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>12392.736</v>
+        <v>7949.448</v>
       </c>
       <c r="M5" t="n">
-        <v>110647.56</v>
+        <v>72755.04119999999</v>
       </c>
       <c r="N5" t="n">
         <v>-1</v>
@@ -774,23 +774,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PSO2500738</t>
+          <t>PSO2500530</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4500575187</v>
+        <v>4500573773</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>SP8523/BNTHB150UZ</t>
+          <t>SP8302/VS221WIW</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1002</v>
+        <v>396</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -800,15 +800,15 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CHILE</t>
+          <t>TAIWAN</t>
         </is>
       </c>
       <c r="H6" s="2" t="n">
-        <v>45874</v>
+        <v>45905</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>P8523-V01-C1201</t>
+          <t>P8302-N01-C1201</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>8845.656000000001</v>
+        <v>2516.184</v>
       </c>
       <c r="M6" t="n">
-        <v>110647.56</v>
+        <v>261924</v>
       </c>
       <c r="N6" t="n">
         <v>-1</v>
@@ -839,19 +839,19 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PSO2500873</t>
+          <t>PSO2500659</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>46159</v>
+        <v>4500574195</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SP5031/CPM-150C</t>
+          <t>SP8341/D212SDE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>300</v>
+        <v>1248</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -865,15 +865,15 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>SAUDI ARABIA</t>
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>45862</v>
+        <v>45853</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>P5031-C01-C1201</t>
+          <t>P8341-S02-C1201</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3576</v>
+        <v>7378.176</v>
       </c>
       <c r="M7" t="n">
-        <v>26104.8</v>
+        <v>53860.6848</v>
       </c>
       <c r="N7" t="n">
         <v>-1</v>
@@ -904,19 +904,19 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PSO2501004</t>
+          <t>PSO2500736</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>835587</v>
+        <v>4500575187</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SP8012/889CGDES</t>
+          <t>SP8530/BNTDHB275UZ</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5184</v>
+        <v>1200</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -930,15 +930,15 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>MEXICO</t>
+          <t>CHILE</t>
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>45872</v>
+        <v>45874</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>P8012-M01-C1204</t>
+          <t>P8530-V03-C1201</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>73954.944</v>
+        <v>15157.2</v>
       </c>
       <c r="M8" t="n">
-        <v>539871.0912</v>
+        <v>110647.56</v>
       </c>
       <c r="N8" t="n">
         <v>-1</v>
@@ -969,19 +969,19 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PSO2501005</t>
+          <t>PSO2500737</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>835587</v>
+        <v>4500575187</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SP8012/889CGDES</t>
+          <t>SP8526/BNTHB300TUZ</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5184</v>
+        <v>1002</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -995,15 +995,15 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>MEXICO</t>
+          <t>CHILE</t>
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>45893</v>
+        <v>45874</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>P8012-M01-C1204</t>
+          <t>P8526-V01-C1203</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1017,10 +1017,10 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>73954.944</v>
+        <v>12392.736</v>
       </c>
       <c r="M9" t="n">
-        <v>539871.0912</v>
+        <v>110647.56</v>
       </c>
       <c r="N9" t="n">
         <v>-1</v>
@@ -1034,19 +1034,19 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PSO2501106</t>
+          <t>PSO2500738</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4500575965</v>
+        <v>4500575187</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2735A-BRUSH50</t>
+          <t>SP8523/BNTHB150UZ</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3000</v>
+        <v>1002</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1060,15 +1060,15 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>BRAZIL</t>
+          <t>CHILE</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>45838</v>
+        <v>45874</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>820-88730054R</t>
+          <t>P8523-V01-C1201</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1082,10 +1082,10 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>8100</v>
+        <v>8845.656000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>59130</v>
+        <v>110647.56</v>
       </c>
       <c r="N10" t="n">
         <v>-1</v>
@@ -1099,19 +1099,19 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PSO2501107</t>
+          <t>PSO2500873</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4500575965</v>
+        <v>46159</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P1200DBR-BRUSH50</t>
+          <t>SP5031/CPM-150C</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3000</v>
+        <v>300</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1125,15 +1125,15 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>BRAZIL</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>45838</v>
+        <v>45862</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>820-85330003R</t>
+          <t>P5031-C01-C1201</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1147,10 +1147,10 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>9000</v>
+        <v>3576</v>
       </c>
       <c r="M11" t="n">
-        <v>59130</v>
+        <v>26104.8</v>
       </c>
       <c r="N11" t="n">
         <v>-1</v>
@@ -1164,19 +1164,19 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PSO2501138</t>
+          <t>PSO2500901</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4500576508</v>
+        <v>4500575721</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SP8019/AS6550E</t>
+          <t>SP8016/BRHD226SDE</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>252</v>
+        <v>2502</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -1194,11 +1194,11 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>45870</v>
+        <v>45884</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>P8019-E02-C1202</t>
+          <t>P8016-S02-C1204</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1212,10 +1212,10 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>6288.66</v>
+        <v>25883.19</v>
       </c>
       <c r="M12" t="n">
-        <v>45907.218</v>
+        <v>162372.294</v>
       </c>
       <c r="N12" t="n">
         <v>-1</v>
@@ -1229,23 +1229,23 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PSO2501190</t>
+          <t>PSO2500902</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4500576530</v>
+        <v>4500575721</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SP8325/279AMZES</t>
+          <t>SP8016/BRHD200SDE</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1255,15 +1255,15 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>MEXICO</t>
+          <t>DUBAI</t>
         </is>
       </c>
       <c r="H13" s="2" t="n">
-        <v>45930</v>
+        <v>45884</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>P8325-M04-C1201</t>
+          <t>P8016-S04-C1201</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1277,10 +1277,10 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>23937.5</v>
+        <v>22242.78</v>
       </c>
       <c r="M13" t="n">
-        <v>174743.75</v>
+        <v>162372.294</v>
       </c>
       <c r="N13" t="n">
         <v>-1</v>
@@ -1294,23 +1294,23 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>PSO2501191</t>
+          <t>PSO2500937</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4500576530</v>
+        <v>4500575970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SP8381/209AMZES</t>
+          <t>SP2573/MT726E</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1320,15 +1320,15 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>MEXICO</t>
+          <t>ROMANIA</t>
         </is>
       </c>
       <c r="H14" s="2" t="n">
-        <v>45930</v>
+        <v>45894</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>P8381-M01-C1201</t>
+          <t>P2573-E01-C1204</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1342,10 +1342,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>17667.5</v>
+        <v>24299.424</v>
       </c>
       <c r="M14" t="n">
-        <v>174743.75</v>
+        <v>460599.2816</v>
       </c>
       <c r="N14" t="n">
         <v>-1</v>
@@ -1359,23 +1359,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>PSO2501221</t>
+          <t>PSO2500978</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4500577162</v>
+        <v>4500575957</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SP8521/BNTHB250UZ</t>
+          <t>SP8510/AS952E</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>360</v>
+        <v>7500</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1385,15 +1385,15 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>URUGUAY</t>
+          <t>FRANCE</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
-        <v>45874</v>
+        <v>45902</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>P8521-V01-C1202</t>
+          <t>P8510-E02-C1202</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1407,10 +1407,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3773.16</v>
+        <v>120570</v>
       </c>
       <c r="M15" t="n">
-        <v>27544.068</v>
+        <v>1140546.0432</v>
       </c>
       <c r="N15" t="n">
         <v>-1</v>
@@ -1424,19 +1424,19 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>PSO2501222</t>
+          <t>PSO2501004</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4500577162</v>
+        <v>835587</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SP8522/BNTHB350UZ</t>
+          <t>SP8012/889CGDES</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>360</v>
+        <v>5184</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1450,15 +1450,15 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>URUGUAY</t>
+          <t>MEXICO</t>
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>45874</v>
+        <v>45872</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>P8522-V02-C1202</t>
+          <t>P8012-M01-C1204</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1472,10 +1472,10 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3911.4</v>
+        <v>73954.944</v>
       </c>
       <c r="M16" t="n">
-        <v>27544.068</v>
+        <v>539871.0912</v>
       </c>
       <c r="N16" t="n">
         <v>-1</v>
@@ -1489,23 +1489,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>PSO2501303</t>
+          <t>PSO2501005</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>702500</v>
+        <v>835587</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SP8875/BC116RAR</t>
+          <t>SP8012/889CGDES</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1104</v>
+        <v>5184</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1515,15 +1515,15 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>ARGENTINA</t>
+          <t>MEXICO</t>
         </is>
       </c>
       <c r="H17" s="2" t="n">
-        <v>45930</v>
+        <v>45893</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>P8875-V04-C1202</t>
+          <t>P8012-M01-C1204</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1537,10 +1537,10 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>11428.608</v>
+        <v>73954.944</v>
       </c>
       <c r="M17" t="n">
-        <v>151110</v>
+        <v>539871.0912</v>
       </c>
       <c r="N17" t="n">
         <v>-1</v>
@@ -1554,23 +1554,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>PSO2501305</t>
+          <t>PSO2501106</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>702503</v>
+        <v>4500575965</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SP8875/BC116RUZ</t>
+          <t>2735A-BRUSH50</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>270</v>
+        <v>3000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1580,15 +1580,15 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>URUGUAY</t>
+          <t>BRAZIL</t>
         </is>
       </c>
       <c r="H18" s="2" t="n">
-        <v>45930</v>
+        <v>45838</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>P8875-V04-C1203</t>
+          <t>820-88730054R</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2700</v>
+        <v>8100</v>
       </c>
       <c r="M18" t="n">
-        <v>43304.184</v>
+        <v>59130</v>
       </c>
       <c r="N18" t="n">
         <v>-1</v>
@@ -1619,19 +1619,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PSO2501307</t>
+          <t>PSO2501107</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4500577626</v>
+        <v>4500575965</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>SP8515/AS136E</t>
+          <t>P1200DBR-BRUSH50</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>180</v>
+        <v>3000</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1645,15 +1645,15 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>DUBAI</t>
+          <t>BRAZIL</t>
         </is>
       </c>
       <c r="H19" s="2" t="n">
-        <v>45873</v>
+        <v>45838</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>P8515-E01-C1202</t>
+          <t>820-85330003R</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1667,10 +1667,10 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2361.06</v>
+        <v>9000</v>
       </c>
       <c r="M19" t="n">
-        <v>17235.738</v>
+        <v>59130</v>
       </c>
       <c r="N19" t="n">
         <v>-1</v>
@@ -1684,19 +1684,19 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>PSO2501323</t>
+          <t>PSO2501117</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4500577352</v>
+        <v>4500576548</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>SP8832/AS86E</t>
+          <t>SP8515/AS136SDE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5400</v>
+        <v>1254</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1710,15 +1710,15 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>FRANCE</t>
+          <t>SAUDI ARABIA</t>
         </is>
       </c>
       <c r="H20" s="2" t="n">
-        <v>45922</v>
+        <v>45915</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>P8832-E02-C1215</t>
+          <t>P8515-S01-C1202</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1732,10 +1732,10 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>30915</v>
+        <v>16565.34</v>
       </c>
       <c r="M20" t="n">
-        <v>225679.5</v>
+        <v>120926.982</v>
       </c>
       <c r="N20" t="n">
         <v>-1</v>
@@ -1749,25 +1749,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PSO2501372</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>702395BUFFER PO</t>
-        </is>
+          <t>PSO2501138</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4500576508</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SP8875/BC116RUZ</t>
+          <t>SP8019/AS6550E</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1002</v>
+        <v>252</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1777,15 +1775,15 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>DUBAI</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>45930</v>
+        <v>45870</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>P8875-V04-C1203</t>
+          <t>P8019-E02-C1202</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1799,10 +1797,10 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>10020</v>
+        <v>6288.66</v>
       </c>
       <c r="M21" t="n">
-        <v>109572.708</v>
+        <v>45907.218</v>
       </c>
       <c r="N21" t="n">
         <v>-1</v>
@@ -1816,19 +1814,19 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PSO2501374</t>
+          <t>PSO2501190</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>702506</v>
+        <v>4500576530</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SP8875/BC116RUZ</t>
+          <t>SP8325/279AMZES</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>552</v>
+        <v>2500</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1842,7 +1840,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PARAGUAY</t>
+          <t>MEXICO</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
@@ -1850,7 +1848,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>P8875-V04-C1203</t>
+          <t>P8325-M04-C1201</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1864,10 +1862,10 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5520</v>
+        <v>23937.5</v>
       </c>
       <c r="M22" t="n">
-        <v>60363.40799999999</v>
+        <v>174743.75</v>
       </c>
       <c r="N22" t="n">
         <v>-1</v>
@@ -1881,19 +1879,19 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PSO2501377</t>
+          <t>PSO2501191</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4500577735</v>
+        <v>4500576530</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SP8893/CD160NN</t>
+          <t>SP8381/209AMZES</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10002</v>
+        <v>2500</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1907,7 +1905,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>USA-MD</t>
+          <t>MEXICO</t>
         </is>
       </c>
       <c r="H23" s="2" t="n">
@@ -1915,7 +1913,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>P8893-L05-C1209</t>
+          <t>P8381-M01-C1201</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1929,10 +1927,10 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>75905.178</v>
+        <v>17667.5</v>
       </c>
       <c r="M23" t="n">
-        <v>1007455.4508</v>
+        <v>174743.75</v>
       </c>
       <c r="N23" t="n">
         <v>-1</v>
@@ -1946,19 +1944,19 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PSO2501384</t>
+          <t>PSO2501221</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>4500577876</v>
+        <v>4500577162</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SP8896/BAB2676TTE</t>
+          <t>SP8521/BNTHB250UZ</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>60</v>
+        <v>360</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1972,15 +1970,15 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>DUBAI</t>
+          <t>URUGUAY</t>
         </is>
       </c>
       <c r="H24" s="2" t="n">
-        <v>45873</v>
+        <v>45874</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>P8896-E02-C1201</t>
+          <t>P8521-V01-C1202</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1994,10 +1992,10 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>513.54</v>
+        <v>3773.16</v>
       </c>
       <c r="M24" t="n">
-        <v>3748.842</v>
+        <v>27544.068</v>
       </c>
       <c r="N24" t="n">
         <v>-1</v>
@@ -2011,19 +2009,19 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PSO2501403</t>
+          <t>PSO2501222</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4500577937</v>
+        <v>4500577162</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SP8526/BNTHB300TUX</t>
+          <t>SP8522/BNTHB350UZ</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>504</v>
+        <v>360</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2037,15 +2035,15 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>COSTA RICA</t>
+          <t>URUGUAY</t>
         </is>
       </c>
       <c r="H25" s="2" t="n">
-        <v>45884</v>
+        <v>45874</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>P8526-L01-C1201</t>
+          <t>P8522-V02-C1202</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2059,10 +2057,10 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5988.528</v>
+        <v>3911.4</v>
       </c>
       <c r="M25" t="n">
-        <v>43716.2544</v>
+        <v>27544.068</v>
       </c>
       <c r="N25" t="n">
         <v>-1</v>
@@ -2076,23 +2074,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PSO2501444</t>
+          <t>PSO2501243</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4500578073</v>
+        <v>4500577209</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SP8893/CD160CES</t>
+          <t>SP8521/BNTHB250UZ</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>4000</v>
+        <v>1368</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2102,15 +2100,15 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>MEXICO</t>
+          <t>PARAGUAY</t>
         </is>
       </c>
       <c r="H26" s="2" t="n">
-        <v>45922</v>
+        <v>45879</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>P8893-M01-C1202</t>
+          <t>P8521-V01-C1204</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2124,10 +2122,10 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>27160</v>
+        <v>14338.008</v>
       </c>
       <c r="M26" t="n">
-        <v>54330.25</v>
+        <v>104667.4584</v>
       </c>
       <c r="N26" t="n">
         <v>-1</v>
@@ -2141,23 +2139,23 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PSO2501445</t>
+          <t>PSO2501255</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4500578073</v>
+        <v>4500577210</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SP8013/303ES</t>
+          <t>SP8521/BNTHB250UZ</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2500</v>
+        <v>1200</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2167,15 +2165,15 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>MEXICO</t>
+          <t>PARAGUAY</t>
         </is>
       </c>
       <c r="H27" s="2" t="n">
-        <v>45922</v>
+        <v>45879</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>P8013-M01-C1201</t>
+          <t>P8521-V01-C1204</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2189,10 +2187,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>11450</v>
+        <v>12577.2</v>
       </c>
       <c r="M27" t="n">
-        <v>54330.25</v>
+        <v>91813.56</v>
       </c>
       <c r="N27" t="n">
         <v>-1</v>
@@ -2206,23 +2204,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PSO2501526</t>
+          <t>PSO2501256</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4500578135</v>
+        <v>4500577210</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SP8875/BC116RAL</t>
+          <t>SP8521/BNTHBPBK250UZ</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>252</v>
+        <v>504</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2232,15 +2230,15 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>COSTA RICA</t>
+          <t>PARAGUAY</t>
         </is>
       </c>
       <c r="H28" s="2" t="n">
-        <v>45930</v>
+        <v>45879</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>P8875-L03-C1204</t>
+          <t>P8521-V01-C1216</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2254,10 +2252,10 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3278.52</v>
+        <v>5124.168</v>
       </c>
       <c r="M28" t="n">
-        <v>28283.85</v>
+        <v>91813.56</v>
       </c>
       <c r="N28" t="n">
         <v>-1</v>
@@ -2271,19 +2269,19 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PSO2501527</t>
+          <t>PSO2501303</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>4500578135</v>
+        <v>702500</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SP8533/P1200DAL</t>
+          <t>SP8875/BC116RAR</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>252</v>
+        <v>1104</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2297,7 +2295,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>COSTA RICA</t>
+          <t>ARGENTINA</t>
         </is>
       </c>
       <c r="H29" s="2" t="n">
@@ -2305,7 +2303,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>P8533-L02-C1201</t>
+          <t>P8875-V04-C1202</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2319,10 +2317,10 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3874.5</v>
+        <v>11428.608</v>
       </c>
       <c r="M29" t="n">
-        <v>28283.85</v>
+        <v>151110</v>
       </c>
       <c r="N29" t="n">
         <v>-1</v>
@@ -2336,19 +2334,19 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PSO2501535</t>
+          <t>PSO2501305</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4500578430</v>
+        <v>702503</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SP8510/AS950E</t>
+          <t>SP8875/BC116RUZ</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3000</v>
+        <v>270</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2362,15 +2360,15 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>INDONESIA</t>
+          <t>URUGUAY</t>
         </is>
       </c>
       <c r="H30" s="2" t="n">
-        <v>45919</v>
+        <v>45930</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>P8510-E02-C1210</t>
+          <t>P8875-V04-C1203</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2384,10 +2382,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>48177</v>
+        <v>2700</v>
       </c>
       <c r="M30" t="n">
-        <v>351692.1</v>
+        <v>43304.184</v>
       </c>
       <c r="N30" t="n">
         <v>-1</v>
@@ -2401,19 +2399,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PSO2501548</t>
+          <t>PSO2501307</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4500575528</v>
+        <v>4500577626</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SP8018/BRHD435SDE</t>
+          <t>SP8515/AS136E</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1752</v>
+        <v>180</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2431,11 +2429,11 @@
         </is>
       </c>
       <c r="H31" s="2" t="n">
-        <v>45884</v>
+        <v>45873</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>P8018-S02-C1201</t>
+          <t>P8515-E01-C1202</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2449,10 +2447,10 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>32189.496</v>
+        <v>2361.06</v>
       </c>
       <c r="M31" t="n">
-        <v>234983.3208</v>
+        <v>17235.738</v>
       </c>
       <c r="N31" t="n">
         <v>-1</v>
@@ -2466,23 +2464,23 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PSO2501549</t>
+          <t>PSO2501323</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4500576551</v>
+        <v>4500577352</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SP8016/BRHD225SDE</t>
+          <t>SP8832/AS86E</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2004</v>
+        <v>5400</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2492,15 +2490,15 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DUBAI</t>
+          <t>FRANCE</t>
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>45884</v>
+        <v>45922</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>P8016-S02-C1201</t>
+          <t>P8832-E02-C1215</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2514,10 +2512,10 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>20613.144</v>
+        <v>30915</v>
       </c>
       <c r="M32" t="n">
-        <v>150475.9512</v>
+        <v>225679.5</v>
       </c>
       <c r="N32" t="n">
         <v>-1</v>
@@ -2531,19 +2529,21 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PSO2501553</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>4500578041</v>
+          <t>PSO2501372</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>702395BUFFER PO</t>
+        </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>D217DSE(00002170)</t>
+          <t>SP8875/BC116RUZ</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>200</v>
+        <v>1002</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -2557,15 +2557,15 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>FRANCE</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="H33" s="2" t="n">
-        <v>45901</v>
+        <v>45930</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>302-82880124R</t>
+          <t>P8875-V04-C1203</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2579,10 +2579,10 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>94</v>
+        <v>10020</v>
       </c>
       <c r="M33" t="n">
-        <v>1591.4</v>
+        <v>109572.708</v>
       </c>
       <c r="N33" t="n">
         <v>-1</v>
@@ -2596,19 +2596,19 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PSO2501554</t>
+          <t>PSO2501374</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4500578557</v>
+        <v>702506</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SP8349/VSD362BA</t>
+          <t>SP8875/BC116RUZ</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2504</v>
+        <v>552</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>PARAGUAY</t>
         </is>
       </c>
       <c r="H34" s="2" t="n">
@@ -2630,7 +2630,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>P8349-A02-C1203</t>
+          <t>P8875-V04-C1203</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>24489.12</v>
+        <v>5520</v>
       </c>
       <c r="M34" t="n">
-        <v>178770.576</v>
+        <v>60363.40799999999</v>
       </c>
       <c r="N34" t="n">
         <v>-1</v>
@@ -2661,19 +2661,19 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PSO2501555</t>
+          <t>PSO2501377</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4500578557</v>
+        <v>4500577735</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SP8395/VSD374A</t>
+          <t>SP8893/CD160NN</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1536</v>
+        <v>10002</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>USA-MD</t>
         </is>
       </c>
       <c r="H35" s="2" t="n">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>P8395-A01-C1201</t>
+          <t>P8893-L05-C1209</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>13814.784</v>
+        <v>75905.178</v>
       </c>
       <c r="M35" t="n">
-        <v>178770.576</v>
+        <v>1007455.4508</v>
       </c>
       <c r="N35" t="n">
         <v>-1</v>
@@ -2726,23 +2726,23 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PSO2501557</t>
+          <t>PSO2501384</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>4500570836</v>
+        <v>4500577876</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SP8012/889CGD</t>
+          <t>SP8896/BAB2676TTE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>19008</v>
+        <v>60</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2752,15 +2752,15 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>USA-GL</t>
+          <t>DUBAI</t>
         </is>
       </c>
       <c r="H36" s="2" t="n">
-        <v>45922</v>
+        <v>45873</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>P8012-L01-C1204</t>
+          <t>P8896-E02-C1201</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2774,10 +2774,10 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>258261.696</v>
+        <v>513.54</v>
       </c>
       <c r="M36" t="n">
-        <v>471327.5952</v>
+        <v>3748.842</v>
       </c>
       <c r="N36" t="n">
         <v>-1</v>
@@ -2791,23 +2791,23 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PSO2501558</t>
+          <t>PSO2501403</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>4500570836</v>
+        <v>4500577937</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SP8012/889CGD</t>
+          <t>SP8526/BNTHB300TUX</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>19008</v>
+        <v>504</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2817,15 +2817,15 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>USA-GL</t>
+          <t>COSTA RICA</t>
         </is>
       </c>
       <c r="H37" s="2" t="n">
-        <v>45929</v>
+        <v>45884</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>P8012-L01-C1204</t>
+          <t>P8526-L01-C1201</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>258261.696</v>
+        <v>5988.528</v>
       </c>
       <c r="M37" t="n">
-        <v>471327.5952</v>
+        <v>43716.2544</v>
       </c>
       <c r="N37" t="n">
         <v>-1</v>
@@ -2856,19 +2856,19 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PSO2501562</t>
+          <t>PSO2501444</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>4500578342</v>
+        <v>4500578073</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SP8022/D6555DU</t>
+          <t>SP8893/CD160CES</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1500</v>
+        <v>4000</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -2882,15 +2882,15 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MEXICO</t>
         </is>
       </c>
       <c r="H38" s="2" t="n">
-        <v>45930</v>
+        <v>45922</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>P8022-E01-C1202</t>
+          <t>P8893-M01-C1202</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2904,10 +2904,10 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>38505</v>
+        <v>27160</v>
       </c>
       <c r="M38" t="n">
-        <v>81045.768</v>
+        <v>54330.25</v>
       </c>
       <c r="N38" t="n">
         <v>-1</v>
@@ -2921,19 +2921,19 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PSO2501568</t>
+          <t>PSO2501445</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4500578342</v>
+        <v>4500578073</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SP8528/2774U</t>
+          <t>SP8013/303ES</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -2947,15 +2947,15 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>MEXICO</t>
         </is>
       </c>
       <c r="H39" s="2" t="n">
-        <v>45930</v>
+        <v>45922</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>P8528-E01-C1201</t>
+          <t>P8013-M01-C1201</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2969,10 +2969,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>46770</v>
+        <v>11450</v>
       </c>
       <c r="M39" t="n">
-        <v>81045.768</v>
+        <v>54330.25</v>
       </c>
       <c r="N39" t="n">
         <v>-1</v>
@@ -2986,19 +2986,19 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PSO2501571</t>
+          <t>PSO2501513</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4500578342</v>
+        <v>46545</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SP2573/7255U</t>
+          <t>SP8343/5549NC</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -3012,15 +3012,15 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H40" s="2" t="n">
-        <v>45930</v>
+        <v>45919</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>P2573-E01-C1201</t>
+          <t>P8343-C01-C1202</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3034,10 +3034,10 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>27447</v>
+        <v>17227.5</v>
       </c>
       <c r="M40" t="n">
-        <v>81045.768</v>
+        <v>247762</v>
       </c>
       <c r="N40" t="n">
         <v>-1</v>
@@ -3051,19 +3051,19 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PSO2501574</t>
+          <t>PSO2501526</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>4500578342</v>
+        <v>4500578135</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SP2388/7498CU</t>
+          <t>SP8875/BC116RAL</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1500</v>
+        <v>252</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>UK</t>
+          <t>COSTA RICA</t>
         </is>
       </c>
       <c r="H41" s="2" t="n">
@@ -3085,7 +3085,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>P2388-E03-C1202</t>
+          <t>P8875-L03-C1204</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3099,10 +3099,10 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>13059</v>
+        <v>3278.52</v>
       </c>
       <c r="M41" t="n">
-        <v>81045.768</v>
+        <v>28283.85</v>
       </c>
       <c r="N41" t="n">
         <v>-1</v>
@@ -3116,19 +3116,19 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PSO2501585</t>
+          <t>PSO2501527</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4500578441</v>
+        <v>4500578135</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>SP8018/BRHD435SDE</t>
+          <t>SP8533/P1200DAL</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1254</v>
+        <v>252</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -3142,7 +3142,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>DUBAI</t>
+          <t>COSTA RICA</t>
         </is>
       </c>
       <c r="H42" s="2" t="n">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>P8018-S02-C1201</t>
+          <t>P8533-L02-C1201</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3164,10 +3164,10 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>23039.742</v>
+        <v>3874.5</v>
       </c>
       <c r="M42" t="n">
-        <v>208271.2338</v>
+        <v>28283.85</v>
       </c>
       <c r="N42" t="n">
         <v>-1</v>
@@ -3181,19 +3181,19 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>PSO2501593</t>
+          <t>PSO2501535</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>4500578341</v>
+        <v>4500578430</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SP8515/AS128SDE</t>
+          <t>SP8510/AS950E</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1002</v>
+        <v>3000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -3207,15 +3207,15 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>DUBAI</t>
+          <t>INDONESIA</t>
         </is>
       </c>
       <c r="H43" s="2" t="n">
-        <v>45929</v>
+        <v>45919</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>P8515-S01-C1208</t>
+          <t>P8510-E02-C1210</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>12555.06</v>
+        <v>48177</v>
       </c>
       <c r="M43" t="n">
-        <v>91651.93799999999</v>
+        <v>351692.1</v>
       </c>
       <c r="N43" t="n">
         <v>-1</v>
@@ -3246,23 +3246,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>PSO2501596</t>
+          <t>PSO2501548</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>46759</v>
+        <v>4500575528</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SP8271/169BIWC</t>
+          <t>SP8018/BRHD435SDE</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2500</v>
+        <v>1752</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3272,15 +3272,15 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>DUBAI</t>
         </is>
       </c>
       <c r="H44" s="2" t="n">
-        <v>45922</v>
+        <v>45884</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>P8271-C02-C1211</t>
+          <t>P8018-S02-C1201</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>17695</v>
+        <v>32189.496</v>
       </c>
       <c r="M44" t="n">
-        <v>129173.5</v>
+        <v>234983.3208</v>
       </c>
       <c r="N44" t="n">
         <v>-1</v>
@@ -3311,23 +3311,23 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>PSO2501608</t>
+          <t>PSO2501549</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4500578641</v>
+        <v>4500576551</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SP8510/AS950E</t>
+          <t>SP8016/BRHD225SDE</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>504</v>
+        <v>2004</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3337,15 +3337,15 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>MALAYSIA</t>
+          <t>DUBAI</t>
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>45919</v>
+        <v>45884</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>P8510-E02-C1201</t>
+          <t>P8016-S02-C1201</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>8093.736</v>
+        <v>20613.144</v>
       </c>
       <c r="M45" t="n">
-        <v>59084.2728</v>
+        <v>150475.9512</v>
       </c>
       <c r="N45" t="n">
         <v>-1</v>
@@ -3376,19 +3376,19 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>PSO2501609</t>
+          <t>PSO2501553</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>46769</v>
+        <v>4500578041</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SP8316/247BWC</t>
+          <t>D217DSE(00002170)</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2500</v>
+        <v>200</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -3402,15 +3402,15 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>FRANCE</t>
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>45930</v>
+        <v>45901</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>P8316-C01-C1203</t>
+          <t>302-82880124R</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -3424,10 +3424,10 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>11762.5</v>
+        <v>94</v>
       </c>
       <c r="M46" t="n">
-        <v>85866.25</v>
+        <v>1591.4</v>
       </c>
       <c r="N46" t="n">
         <v>-1</v>
@@ -3441,19 +3441,19 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PSO2501624</t>
+          <t>PSO2501554</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>46587</v>
+        <v>4500578557</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SP8286/246LC</t>
+          <t>SP8349/VSD362BA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>3501</v>
+        <v>2504</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -3467,15 +3467,15 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>P8286-C02-C1227</t>
+          <t>P8349-A02-C1203</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3489,10 +3489,10 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>17074.377</v>
+        <v>24489.12</v>
       </c>
       <c r="M47" t="n">
-        <v>124642.9521</v>
+        <v>178770.576</v>
       </c>
       <c r="N47" t="n">
         <v>-1</v>
@@ -3506,19 +3506,19 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>PSO2501625</t>
+          <t>PSO2501555</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>46587</v>
+        <v>4500578557</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>SP8328/289LC</t>
+          <t>SP8395/VSD374A</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2500</v>
+        <v>1536</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -3532,15 +3532,15 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H48" s="2" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>P8328-C01-C1205</t>
+          <t>P8395-A01-C1201</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3554,10 +3554,10 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>15882.5</v>
+        <v>13814.784</v>
       </c>
       <c r="M48" t="n">
-        <v>124642.9521</v>
+        <v>178770.576</v>
       </c>
       <c r="N48" t="n">
         <v>-1</v>
@@ -3571,19 +3571,19 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>PSO2501626</t>
+          <t>PSO2501557</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>46584</v>
+        <v>4500570836</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SP8392/910NC</t>
+          <t>SP8012/889CGD</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>3500</v>
+        <v>19008</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -3597,15 +3597,15 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>USA-GL</t>
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>45929</v>
+        <v>45922</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>P8392-C01-C1220</t>
+          <t>P8012-L01-C1204</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3619,10 +3619,10 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>39427.5</v>
+        <v>258261.696</v>
       </c>
       <c r="M49" t="n">
-        <v>287820.75</v>
+        <v>471327.5952</v>
       </c>
       <c r="N49" t="n">
         <v>-1</v>
@@ -3636,19 +3636,19 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>PSO2501634</t>
+          <t>PSO2501558</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4500578709</v>
+        <v>4500570836</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SP8873/VS2735GA</t>
+          <t>SP8012/889CGD</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1500</v>
+        <v>19008</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -3662,15 +3662,15 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>USA-GL</t>
         </is>
       </c>
       <c r="H50" s="2" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>P8873-A02-C1202</t>
+          <t>P8012-L01-C1204</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3684,10 +3684,10 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>24642</v>
+        <v>258261.696</v>
       </c>
       <c r="M50" t="n">
-        <v>179886.6</v>
+        <v>471327.5952</v>
       </c>
       <c r="N50" t="n">
         <v>-1</v>
@@ -3701,21 +3701,19 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>PSO2501638</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>IP-0016(175726)</t>
-        </is>
+          <t>PSO2501562</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>4500578342</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SP3855/SSW10C(70-0120.2)</t>
+          <t>SP8022/D6555DU</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>6306</v>
+        <v>1500</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -3729,7 +3727,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="H51" s="2" t="n">
@@ -3737,7 +3735,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>P3855-C01-C1201</t>
+          <t>P8022-E01-C1202</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3751,10 +3749,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>44015.88</v>
+        <v>38505</v>
       </c>
       <c r="M51" t="n">
-        <v>321315.924</v>
+        <v>81045.768</v>
       </c>
       <c r="N51" t="n">
         <v>-1</v>
@@ -3768,21 +3766,19 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>PSO2501641</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>IP-0017(175727)</t>
-        </is>
+          <t>PSO2501568</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>4500578342</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SP3858/SSW12C(814116)</t>
+          <t>SP8528/2774U</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4578</v>
+        <v>3000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -3796,7 +3792,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="H52" s="2" t="n">
@@ -3804,7 +3800,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>P3858-C01-C1201</t>
+          <t>P8528-E01-C1201</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -3818,10 +3814,10 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>33648.3</v>
+        <v>46770</v>
       </c>
       <c r="M52" t="n">
-        <v>245632.59</v>
+        <v>81045.768</v>
       </c>
       <c r="N52" t="n">
         <v>-1</v>
@@ -3835,19 +3831,19 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PSO2501643</t>
+          <t>PSO2501571</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>46587</v>
+        <v>4500578342</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SP8875/BC125DBC</t>
+          <t>SP2573/7255U</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -3861,15 +3857,15 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="H53" s="2" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>P8875-C01-C1218</t>
+          <t>P2573-E01-C1201</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -3883,10 +3879,10 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>29257.5</v>
+        <v>27447</v>
       </c>
       <c r="M53" t="n">
-        <v>124642.9521</v>
+        <v>81045.768</v>
       </c>
       <c r="N53" t="n">
         <v>-1</v>
@@ -3900,19 +3896,19 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>PSO2501644</t>
+          <t>PSO2501574</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>46587</v>
+        <v>4500578342</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SP8878/BC80QSDMC</t>
+          <t>SP2388/7498CU</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2502</v>
+        <v>1500</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -3926,15 +3922,15 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>UK</t>
         </is>
       </c>
       <c r="H54" s="2" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>P8878-C01-C1202</t>
+          <t>P2388-E03-C1202</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -3948,10 +3944,10 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>19405.512</v>
+        <v>13059</v>
       </c>
       <c r="M54" t="n">
-        <v>124642.9521</v>
+        <v>81045.768</v>
       </c>
       <c r="N54" t="n">
         <v>-1</v>
@@ -3965,19 +3961,19 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>PSO2501649</t>
+          <t>PSO2501585</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4500579004</v>
+        <v>4500578441</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SP8521/BNTHBLV250UZ-PP44</t>
+          <t>SP8018/BRHD435SDE</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>504</v>
+        <v>1254</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -3991,15 +3987,15 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>MILLPLAN(PARAGUAY)</t>
+          <t>DUBAI</t>
         </is>
       </c>
       <c r="H55" s="2" t="n">
-        <v>45924</v>
+        <v>45930</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>P8521-V01-C1220</t>
+          <t>P8018-S02-C1201</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4013,10 +4009,10 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>4901.904</v>
+        <v>23039.742</v>
       </c>
       <c r="M55" t="n">
-        <v>35783.8992</v>
+        <v>208271.2338</v>
       </c>
       <c r="N55" t="n">
         <v>-1</v>
@@ -4030,19 +4026,19 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>PSO2501652</t>
+          <t>PSO2501593</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4500579098</v>
+        <v>4500578341</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AS136SDE-GB</t>
+          <t>SP8515/AS128SDE</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>7</v>
+        <v>1002</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -4056,7 +4052,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>KUWAIT</t>
+          <t>DUBAI</t>
         </is>
       </c>
       <c r="H56" s="2" t="n">
@@ -4064,7 +4060,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>P8515-S01-C1202</t>
+          <t>P8515-S01-C1208</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4078,10 +4074,10 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>92.47</v>
+        <v>12555.06</v>
       </c>
       <c r="M56" t="n">
-        <v>353.8675</v>
+        <v>91651.93799999999</v>
       </c>
       <c r="N56" t="n">
         <v>-1</v>
@@ -4095,19 +4091,19 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>PSO2501653</t>
+          <t>PSO2501596</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4500579099</v>
+        <v>46759</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SP8875/AS115SDE</t>
+          <t>SP8271/169BIWC</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2502</v>
+        <v>2500</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -4121,15 +4117,15 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>DUBAI</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H57" s="2" t="n">
-        <v>45929</v>
+        <v>45922</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>P8875-S03-C1202</t>
+          <t>P8271-C02-C1211</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4143,10 +4139,10 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>29756.286</v>
+        <v>17695</v>
       </c>
       <c r="M57" t="n">
-        <v>106160.25</v>
+        <v>129173.5</v>
       </c>
       <c r="N57" t="n">
         <v>-1</v>
@@ -4160,19 +4156,19 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PSO2501655</t>
+          <t>PSO2501608</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4500579099</v>
+        <v>4500578641</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SP8515/AS136SDE</t>
+          <t>SP8510/AS950E</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1500</v>
+        <v>504</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -4186,15 +4182,15 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>DUBAI</t>
+          <t>MALAYSIA</t>
         </is>
       </c>
       <c r="H58" s="2" t="n">
-        <v>45929</v>
+        <v>45919</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>P8515-S01-C1202</t>
+          <t>P8510-E02-C1201</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4208,10 +4204,10 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>19815</v>
+        <v>8093.736</v>
       </c>
       <c r="M58" t="n">
-        <v>106160.25</v>
+        <v>59084.2728</v>
       </c>
       <c r="N58" t="n">
         <v>-1</v>
@@ -4225,19 +4221,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PSO2501663</t>
+          <t>PSO2501609</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>4500579134</v>
+        <v>46769</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>SP8873/AS200E</t>
+          <t>SP8316/247BWC</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11400</v>
+        <v>2500</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -4251,7 +4247,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>FRANCE</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H59" s="2" t="n">
@@ -4259,7 +4255,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>P8873-E02-C1206</t>
+          <t>P8316-C01-C1203</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4273,10 +4269,10 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>173998.2</v>
+        <v>11762.5</v>
       </c>
       <c r="M59" t="n">
-        <v>1270186.86</v>
+        <v>85866.25</v>
       </c>
       <c r="N59" t="n">
         <v>-1</v>
@@ -4290,19 +4286,19 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PSO2501665</t>
+          <t>PSO2501624</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>4500579134</v>
+        <v>46587</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>SP8873/AS965E</t>
+          <t>SP8286/246LC</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4200</v>
+        <v>3501</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -4316,15 +4312,15 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>FRANCE</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H60" s="2" t="n">
-        <v>45930</v>
+        <v>45929</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>P8873-E03-C1206</t>
+          <t>P8286-C02-C1227</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4338,10 +4334,10 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>77683.2</v>
+        <v>17074.377</v>
       </c>
       <c r="M60" t="n">
-        <v>1270186.86</v>
+        <v>124642.9521</v>
       </c>
       <c r="N60" t="n">
         <v>-1</v>
@@ -4355,19 +4351,19 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>PSO2501678</t>
+          <t>PSO2501625</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>204108</v>
+        <v>46587</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SP8291/BNT5548</t>
+          <t>SP8328/289LC</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>504</v>
+        <v>2500</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -4381,15 +4377,15 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>USA-GL</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H61" s="2" t="n">
-        <v>45901</v>
+        <v>45929</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>P8291-L05-C1251</t>
+          <t>P8328-C01-C1205</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4403,10 +4399,10 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>6060.6</v>
+        <v>15882.5</v>
       </c>
       <c r="M61" t="n">
-        <v>465551.7768</v>
+        <v>124642.9521</v>
       </c>
       <c r="N61" t="n">
         <v>-1</v>
@@ -4420,23 +4416,23 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>RSO2500027</t>
+          <t>PSO2501626</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>835580</v>
+        <v>46584</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SP8316/257TN</t>
+          <t>SP8392/910NC</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>9672</v>
+        <v>3500</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4446,15 +4442,15 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H62" s="2" t="n">
-        <v>45870</v>
+        <v>45929</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>P8316-L01-R1209</t>
+          <t>P8392-C01-C1220</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4468,10 +4464,10 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>62065.224</v>
+        <v>39427.5</v>
       </c>
       <c r="M62" t="n">
-        <v>453076.1352</v>
+        <v>287820.75</v>
       </c>
       <c r="N62" t="n">
         <v>-1</v>
@@ -4485,19 +4481,19 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>RSO2500045</t>
+          <t>PSO2501634</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4500578073</v>
+        <v>4500578709</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SP9319/FB27WES</t>
+          <t>SP8873/VS2735GA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -4511,15 +4507,15 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>MEXICO</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H63" s="2" t="n">
-        <v>45922</v>
+        <v>45925</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>P9319-M01-C1201</t>
+          <t>P8873-A02-C1202</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4533,10 +4529,10 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>23955</v>
+        <v>24642</v>
       </c>
       <c r="M63" t="n">
-        <v>54330.25</v>
+        <v>179886.6</v>
       </c>
       <c r="N63" t="n">
         <v>-1</v>
@@ -4550,19 +4546,21 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>RSO2500051</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>4500578135</v>
+          <t>PSO2501638</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>IP-0016(175726)</t>
+        </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SP9305/FB3SBES</t>
+          <t>SP3855/SSW10C(70-0120.2)</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>200</v>
+        <v>6306</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -4576,7 +4574,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>COSTA RICA</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="H64" s="2" t="n">
@@ -4584,7 +4582,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>P9305-M07-C1202</t>
+          <t>P3855-C01-C1201</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4598,10 +4596,10 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1619.4</v>
+        <v>44015.88</v>
       </c>
       <c r="M64" t="n">
-        <v>28283.85</v>
+        <v>321315.924</v>
       </c>
       <c r="N64" t="n">
         <v>-1</v>
@@ -4615,23 +4613,25 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SP2501371</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>4500577823</v>
+          <t>PSO2501641</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>IP-0017(175727)</t>
+        </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SP8525/BC114RDC-DBLCRKTDR</t>
+          <t>SP3858/SSW12C(814116)</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>9360</v>
+        <v>4578</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4641,15 +4641,15 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>DG-GOLD EDGE</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="H65" s="2" t="n">
-        <v>45891</v>
+        <v>45930</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>P8525-C01-C1207</t>
+          <t>P3858-C01-C1201</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4663,10 +4663,10 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>83809.44</v>
+        <v>33648.3</v>
       </c>
       <c r="M65" t="n">
-        <v>611808.912</v>
+        <v>245632.59</v>
       </c>
       <c r="N65" t="n">
         <v>-1</v>
@@ -4680,41 +4680,41 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TSO2500039</t>
+          <t>PSO2501643</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>204053</v>
+        <v>46587</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SP8005/BNT9100</t>
+          <t>SP8875/BC125DBC</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>600</v>
+        <v>2500</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>USA-GL</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H66" s="2" t="n">
-        <v>45825</v>
+        <v>45929</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>P8005-L01-T1201</t>
+          <t>P8875-C01-C1218</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>16698</v>
+        <v>29257.5</v>
       </c>
       <c r="M66" t="n">
-        <v>121895.4</v>
+        <v>124642.9521</v>
       </c>
       <c r="N66" t="n">
         <v>-1</v>
@@ -4745,41 +4745,41 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TSO2500043</t>
+          <t>PSO2501644</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>4500574528</v>
+        <v>46587</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SP8875/BC120</t>
+          <t>SP8878/BC80QSDMC</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>114</v>
+        <v>2502</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>USA-MD</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H67" s="2" t="n">
-        <v>45870</v>
+        <v>45929</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>P8875-L01-T1204</t>
+          <t>P8878-C01-C1202</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -4793,10 +4793,10 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1262.436</v>
+        <v>19405.512</v>
       </c>
       <c r="M67" t="n">
-        <v>9215.782799999999</v>
+        <v>124642.9521</v>
       </c>
       <c r="N67" t="n">
         <v>-1</v>
@@ -4810,41 +4810,41 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TSO2500048</t>
+          <t>PSO2501649</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>4500574866</v>
+        <v>4500579004</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SP8228/BHOSPBK6689</t>
+          <t>SP8521/BNTHBLV250UZ-PP44</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>168</v>
+        <v>504</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>USA-MD</t>
+          <t>MILLPLAN(PARAGUAY)</t>
         </is>
       </c>
       <c r="H68" s="2" t="n">
-        <v>45879</v>
+        <v>45924</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>P8228-L05-T1201</t>
+          <t>P8521-V01-C1220</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -4858,10 +4858,10 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>2519.832</v>
+        <v>4901.904</v>
       </c>
       <c r="M68" t="n">
-        <v>18394.7736</v>
+        <v>35783.8992</v>
       </c>
       <c r="N68" t="n">
         <v>-1</v>
@@ -4875,41 +4875,41 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TSO2500059</t>
+          <t>PSO2501652</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4500574776</v>
+        <v>4500579098</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SP8289/121KW</t>
+          <t>AS136SDE-GB</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5000</v>
+        <v>7</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>USA-GL</t>
+          <t>KUWAIT</t>
         </is>
       </c>
       <c r="H69" s="2" t="n">
-        <v>45872</v>
+        <v>45929</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>P8289-L02-T1214</t>
+          <t>P8515-S01-C1202</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -4923,10 +4923,10 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>52490</v>
+        <v>92.47</v>
       </c>
       <c r="M69" t="n">
-        <v>383177</v>
+        <v>353.8675</v>
       </c>
       <c r="N69" t="n">
         <v>-1</v>
@@ -4940,41 +4940,41 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TSO2500062</t>
+          <t>PSO2501653</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>4500574943</v>
+        <v>4500579099</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SP5003/TOB-260N1NAS</t>
+          <t>SP8875/AS115SDE</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1000</v>
+        <v>2502</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>USA-GL</t>
+          <t>DUBAI</t>
         </is>
       </c>
       <c r="H70" s="2" t="n">
-        <v>45838</v>
+        <v>45929</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>P5003-L03-T1203</t>
+          <t>P8875-S03-C1202</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>71730</v>
+        <v>29756.286</v>
       </c>
       <c r="M70" t="n">
-        <v>523629</v>
+        <v>106160.25</v>
       </c>
       <c r="N70" t="n">
         <v>-1</v>
@@ -5005,41 +5005,41 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TSO2500067</t>
+          <t>PSO2501655</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>4500575133</v>
+        <v>4500579099</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SP8660/134NR</t>
+          <t>SP8515/AS136SDE</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>9000</v>
+        <v>1500</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>USA-MD</t>
+          <t>DUBAI</t>
         </is>
       </c>
       <c r="H71" s="2" t="n">
-        <v>45884</v>
+        <v>45929</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>P8660-L03-T1205</t>
+          <t>P8515-S01-C1202</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5053,10 +5053,10 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>102870</v>
+        <v>19815</v>
       </c>
       <c r="M71" t="n">
-        <v>702995.84</v>
+        <v>106160.25</v>
       </c>
       <c r="N71" t="n">
         <v>-1</v>
@@ -5070,19 +5070,19 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TSO2500071</t>
+          <t>PSO2501663</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>4500575133</v>
+        <v>4500579134</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SP8325/259WMTY</t>
+          <t>SP8873/AS200E</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>8000</v>
+        <v>11400</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -5091,20 +5091,20 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>USA-MD</t>
+          <t>FRANCE</t>
         </is>
       </c>
       <c r="H72" s="2" t="n">
-        <v>45905</v>
+        <v>45930</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>P8325-L04-T1201</t>
+          <t>P8873-E02-C1206</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5118,10 +5118,10 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>94504</v>
+        <v>173998.2</v>
       </c>
       <c r="M72" t="n">
-        <v>702995.84</v>
+        <v>1270186.86</v>
       </c>
       <c r="N72" t="n">
         <v>-1</v>
@@ -5135,41 +5135,41 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TSO2500073</t>
+          <t>PSO2501665</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4500575081</v>
+        <v>4500579134</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SP5013/TOB-135NNAS</t>
+          <t>SP8873/AS965E</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>280</v>
+        <v>4200</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>USA-GL</t>
+          <t>FRANCE</t>
         </is>
       </c>
       <c r="H73" s="2" t="n">
-        <v>45833</v>
+        <v>45930</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>P5013-L03-T1203</t>
+          <t>P8873-E03-C1206</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5183,10 +5183,10 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>12140.8</v>
+        <v>77683.2</v>
       </c>
       <c r="M73" t="n">
-        <v>88627.84</v>
+        <v>1270186.86</v>
       </c>
       <c r="N73" t="n">
         <v>-1</v>
@@ -5200,28 +5200,28 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TSO2500090</t>
+          <t>PSO2501678</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>4500575810</v>
+        <v>204108</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SP8381/209TGN</t>
+          <t>SP8291/BNT5548</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>6000</v>
+        <v>504</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -5230,11 +5230,11 @@
         </is>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45894</v>
+        <v>45901</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>P8381-L01-T1204</t>
+          <t>P8291-L05-C1251</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>58800</v>
+        <v>6060.6</v>
       </c>
       <c r="M74" t="n">
-        <v>407595.5</v>
+        <v>465551.7768</v>
       </c>
       <c r="N74" t="n">
         <v>-1</v>
@@ -5265,19 +5265,19 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TSO2500091</t>
+          <t>PSO2501679</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>4500575810</v>
+        <v>204108</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SP8381/209TPN</t>
+          <t>SP8521/BNTHB250</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>5000</v>
+        <v>720</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5295,11 +5295,11 @@
         </is>
       </c>
       <c r="H75" s="2" t="n">
-        <v>45881</v>
+        <v>45888</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>P8381-L01-T1206</t>
+          <t>P8521-L01-C1255</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5313,10 +5313,10 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>49000</v>
+        <v>11100.24</v>
       </c>
       <c r="M75" t="n">
-        <v>407595.5</v>
+        <v>465551.7768</v>
       </c>
       <c r="N75" t="n">
         <v>-1</v>
@@ -5330,19 +5330,19 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TSO2500092</t>
+          <t>RSO2500027</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>4500575810</v>
+        <v>835580</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SP8316/247TPW</t>
+          <t>SP8316/257TN</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>8000</v>
+        <v>9672</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -5351,20 +5351,20 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>USA-MD</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="H76" s="2" t="n">
-        <v>45889</v>
+        <v>45870</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>P8316-L01-T1202</t>
+          <t>P8316-L01-R1209</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5378,10 +5378,10 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>56336</v>
+        <v>62065.224</v>
       </c>
       <c r="M76" t="n">
-        <v>407595.5</v>
+        <v>453076.1352</v>
       </c>
       <c r="N76" t="n">
         <v>-1</v>
@@ -5395,19 +5395,19 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TSO2500093</t>
+          <t>RSO2500028</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>4500575810</v>
+        <v>835580</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SP8325/259WMTY</t>
+          <t>SP8316/257TN</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>6000</v>
+        <v>14176</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -5416,20 +5416,20 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>USA-MD</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="H77" s="2" t="n">
-        <v>45884</v>
+        <v>45881</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>P8325-L04-T1201</t>
+          <t>P8316-L01-R1209</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5443,10 +5443,10 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>70878</v>
+        <v>90967.39200000001</v>
       </c>
       <c r="M77" t="n">
-        <v>407595.5</v>
+        <v>453076.1352</v>
       </c>
       <c r="N77" t="n">
         <v>-1</v>
@@ -5460,19 +5460,19 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TSO2500094</t>
+          <t>RSO2500044</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>4500575810</v>
+        <v>4500578073</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SP8006/566DCX</t>
+          <t>SP9305/FB3SBES</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5000</v>
+        <v>2800</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -5481,20 +5481,20 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>USA-GL</t>
+          <t>MEXICO</t>
         </is>
       </c>
       <c r="H78" s="2" t="n">
-        <v>45915</v>
+        <v>45922</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>P8006-L01-T1207</t>
+          <t>P9305-M07-C1202</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5508,10 +5508,10 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>46440</v>
+        <v>22671.6</v>
       </c>
       <c r="M78" t="n">
-        <v>407595.5</v>
+        <v>54330.25</v>
       </c>
       <c r="N78" t="n">
         <v>-1</v>
@@ -5525,41 +5525,41 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TSO2500095</t>
+          <t>RSO2500045</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>4500575810</v>
+        <v>4500578073</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SP8012/888</t>
+          <t>SP9319/FB27WES</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>USA-GL</t>
+          <t>MEXICO</t>
         </is>
       </c>
       <c r="H79" s="2" t="n">
-        <v>45898</v>
+        <v>45922</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>P8012-L01-T1201</t>
+          <t>P9319-M01-C1201</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5573,10 +5573,10 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>150470</v>
+        <v>23955</v>
       </c>
       <c r="M79" t="n">
-        <v>407595.5</v>
+        <v>54330.25</v>
       </c>
       <c r="N79" t="n">
         <v>-1</v>
@@ -5590,41 +5590,41 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TSO2500124</t>
+          <t>RSO2500051</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>4500575810</v>
+        <v>4500578135</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SP8381/209BCX</t>
+          <t>SP9305/FB3SBES</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10000</v>
+        <v>200</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>8月</t>
+          <t>9月</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>USA-GL</t>
+          <t>COSTA RICA</t>
         </is>
       </c>
       <c r="H80" s="2" t="n">
-        <v>45894</v>
+        <v>45930</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>P8381-L01-T1205</t>
+          <t>P9305-M07-C1202</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5638,10 +5638,10 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>97510</v>
+        <v>1619.4</v>
       </c>
       <c r="M80" t="n">
-        <v>407595.5</v>
+        <v>28283.85</v>
       </c>
       <c r="N80" t="n">
         <v>-1</v>
@@ -5655,19 +5655,19 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TSO2500170</t>
+          <t>RSO2500063</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>4500576228</v>
+        <v>835615</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SP2583/HC244CM</t>
+          <t>SP8026/305</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>2000</v>
+        <v>11776</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -5676,20 +5676,20 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>USA-MD</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="H81" s="2" t="n">
-        <v>45930</v>
+        <v>45926</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>P2583-L01-T1208</t>
+          <t>P8026-L01-R1201</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -5703,10 +5703,10 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>11526</v>
+        <v>70656</v>
       </c>
       <c r="M81" t="n">
-        <v>336559.2</v>
+        <v>515788.8</v>
       </c>
       <c r="N81" t="n">
         <v>-1</v>
@@ -5720,41 +5720,41 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TSO2500171</t>
+          <t>SP2501371</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>4500576228</v>
+        <v>4500577823</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SP2583/HC244CM</t>
+          <t>SP8525/BC114RDC-DBLCRKTDR</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>8000</v>
+        <v>9360</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>9月</t>
+          <t>8月</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>柬埔寨</t>
+          <t>国内</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>USA-GL</t>
+          <t>DG-GOLD EDGE</t>
         </is>
       </c>
       <c r="H82" s="2" t="n">
-        <v>45930</v>
+        <v>45891</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>P2583-L01-T1208</t>
+          <t>P8525-C01-C1207</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -5768,10 +5768,10 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>46104</v>
+        <v>83809.44</v>
       </c>
       <c r="M82" t="n">
-        <v>336559.2</v>
+        <v>611808.912</v>
       </c>
       <c r="N82" t="n">
         <v>-1</v>
@@ -5785,19 +5785,19 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TSO2500177</t>
+          <t>TSO2500039</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>4500576656</v>
+        <v>204053</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SP8316/247BW</t>
+          <t>SP8005/BNT9100</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>3996</v>
+        <v>600</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -5815,11 +5815,11 @@
         </is>
       </c>
       <c r="H83" s="2" t="n">
-        <v>45895</v>
+        <v>45825</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>P8316-L01-T1203</t>
+          <t>P8005-L01-T1201</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -5833,10 +5833,10 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>27428.544</v>
+        <v>16698</v>
       </c>
       <c r="M83" t="n">
-        <v>200228.3712</v>
+        <v>121895.4</v>
       </c>
       <c r="N83" t="n">
         <v>-1</v>
@@ -5850,19 +5850,19 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TSO2500181</t>
+          <t>TSO2500043</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>4500576656</v>
+        <v>4500574528</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SP8316/247W</t>
+          <t>SP8875/BC120</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>3204</v>
+        <v>114</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -5876,15 +5876,15 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>USA-GL</t>
+          <t>USA-MD</t>
         </is>
       </c>
       <c r="H84" s="2" t="n">
-        <v>45891</v>
+        <v>45870</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>P8316-L01-T1204</t>
+          <t>P8875-L01-T1204</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -5898,10 +5898,10 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>21992.256</v>
+        <v>1262.436</v>
       </c>
       <c r="M84" t="n">
-        <v>200228.3712</v>
+        <v>9215.782799999999</v>
       </c>
       <c r="N84" t="n">
         <v>-1</v>
@@ -5915,19 +5915,19 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>TSO2500182</t>
+          <t>TSO2500048</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4500576656</v>
+        <v>4500574866</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SP8660/134W</t>
+          <t>SP8228/BHOSPBK6689</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>996</v>
+        <v>168</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -5941,15 +5941,15 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>USA-GL</t>
+          <t>USA-MD</t>
         </is>
       </c>
       <c r="H85" s="2" t="n">
-        <v>45885</v>
+        <v>45879</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>P8660-L03-T1202</t>
+          <t>P8228-L05-T1201</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -5963,10 +5963,10 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>11100.42</v>
+        <v>2519.832</v>
       </c>
       <c r="M85" t="n">
-        <v>200228.3712</v>
+        <v>18394.7736</v>
       </c>
       <c r="N85" t="n">
         <v>-1</v>
@@ -5980,63 +5980,3313 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>TSO2500054</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>4500574776</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SP8325/259WMTY</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>P8325-L04-T1201</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>59065</v>
+      </c>
+      <c r="M86" t="n">
+        <v>383177</v>
+      </c>
+      <c r="N86" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TSO2500056</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>4500574776</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SP8325/259WMTY</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>USA-MD</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>45878</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>P8325-L04-T1201</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>11541</v>
+      </c>
+      <c r="M87" t="n">
+        <v>383177</v>
+      </c>
+      <c r="N87" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TSO2500059</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>4500574776</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SP8289/121KW</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>45872</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>P8289-L02-T1214</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>52490</v>
+      </c>
+      <c r="M88" t="n">
+        <v>383177</v>
+      </c>
+      <c r="N88" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>TSO2500062</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>4500574943</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SP5003/TOB-260N1NAS</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>P5003-L03-T1203</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>71730</v>
+      </c>
+      <c r="M89" t="n">
+        <v>523629</v>
+      </c>
+      <c r="N89" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>TSO2500067</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>4500575133</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SP8660/134NR</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>USA-MD</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>P8660-L03-T1205</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>102870</v>
+      </c>
+      <c r="M90" t="n">
+        <v>702995.84</v>
+      </c>
+      <c r="N90" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TSO2500068</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>4500575133</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SP8012/888</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>3600</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>USA-MD</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>P8012-L01-T1201</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>54169.2</v>
+      </c>
+      <c r="M91" t="n">
+        <v>702995.84</v>
+      </c>
+      <c r="N91" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>TSO2500069</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>4500575133</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SP8012/888</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>6400</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>USA-MD</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>45871</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>P8012-L01-T1201</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>96300.8</v>
+      </c>
+      <c r="M92" t="n">
+        <v>702995.84</v>
+      </c>
+      <c r="N92" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TSO2500071</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>4500575133</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SP8325/259WMTY</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>USA-MD</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>45905</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>P8325-L04-T1201</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>94504</v>
+      </c>
+      <c r="M93" t="n">
+        <v>702995.84</v>
+      </c>
+      <c r="N93" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TSO2500072</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>4500575133</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SP8012/888</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>45899</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>P8012-L01-T1201</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>150470</v>
+      </c>
+      <c r="M94" t="n">
+        <v>702995.84</v>
+      </c>
+      <c r="N94" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TSO2500073</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>4500575081</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SP5013/TOB-135NNAS</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>280</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>45833</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>P5013-L03-T1203</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>12140.8</v>
+      </c>
+      <c r="M95" t="n">
+        <v>88627.84</v>
+      </c>
+      <c r="N95" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>TSO2500089</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>4500575810</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SP8660/134NR</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>45873</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>P8660-L03-T1205</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>55835</v>
+      </c>
+      <c r="M96" t="n">
+        <v>407595.5</v>
+      </c>
+      <c r="N96" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>TSO2500090</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>4500575810</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SP8381/209TGN</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>P8381-L01-T1204</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>58800</v>
+      </c>
+      <c r="M97" t="n">
+        <v>407595.5</v>
+      </c>
+      <c r="N97" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>TSO2500091</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>4500575810</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SP8381/209TPN</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>45881</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>P8381-L01-T1206</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>49000</v>
+      </c>
+      <c r="M98" t="n">
+        <v>407595.5</v>
+      </c>
+      <c r="N98" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>TSO2500092</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>4500575810</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SP8316/247TPW</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>USA-MD</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>P8316-L01-T1202</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>56336</v>
+      </c>
+      <c r="M99" t="n">
+        <v>407595.5</v>
+      </c>
+      <c r="N99" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>TSO2500093</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>4500575810</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>SP8325/259WMTY</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>USA-MD</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>45884</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>P8325-L04-T1201</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>70878</v>
+      </c>
+      <c r="M100" t="n">
+        <v>407595.5</v>
+      </c>
+      <c r="N100" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>TSO2500094</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>4500575810</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>SP8006/566DCX</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>45915</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>P8006-L01-T1207</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>46440</v>
+      </c>
+      <c r="M101" t="n">
+        <v>407595.5</v>
+      </c>
+      <c r="N101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>TSO2500095</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>4500575810</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SP8012/888</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>45898</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>P8012-L01-T1201</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>150470</v>
+      </c>
+      <c r="M102" t="n">
+        <v>407595.5</v>
+      </c>
+      <c r="N102" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>TSO2500124</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>4500575810</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SP8381/209BCX</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>45894</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>P8381-L01-T1205</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>97510</v>
+      </c>
+      <c r="M103" t="n">
+        <v>407595.5</v>
+      </c>
+      <c r="N103" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>TSO2500125</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>4500575810</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SP8372/420NR</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>USA-MD</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>45888</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>P8372-L01-T1206</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>33435</v>
+      </c>
+      <c r="M104" t="n">
+        <v>407595.5</v>
+      </c>
+      <c r="N104" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>TSO2500126</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>4500575810</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SP8392/910NR</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>USA-MD</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>P8392-L03-T1212</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>74025</v>
+      </c>
+      <c r="M105" t="n">
+        <v>407595.5</v>
+      </c>
+      <c r="N105" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>TSO2500127</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>4500575810</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SP8019/998L</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>45913</v>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>P8019-L01-T1205</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>83640</v>
+      </c>
+      <c r="M106" t="n">
+        <v>407595.5</v>
+      </c>
+      <c r="N106" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>TSO2500156</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>4500576017</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SP8535/BC610</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>45922</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>P8535-L01-T1201</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>71280</v>
+      </c>
+      <c r="M107" t="n">
+        <v>520344</v>
+      </c>
+      <c r="N107" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>TSO2500157</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>4500576017</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SP8535/BC610</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>45929</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>P8535-L01-T1201</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>59400</v>
+      </c>
+      <c r="M108" t="n">
+        <v>520344</v>
+      </c>
+      <c r="N108" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>TSO2500162</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>4500576103</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SP8532/BC95</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>USA-MD</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>45912</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>P8532-L01-T1201</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>87710</v>
+      </c>
+      <c r="M109" t="n">
+        <v>721429.7999999999</v>
+      </c>
+      <c r="N109" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>TSO2500163</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>4500576103</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SP8875/BC118R</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>45920</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>P8875-L01-T1206</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>75084</v>
+      </c>
+      <c r="M110" t="n">
+        <v>721429.7999999999</v>
+      </c>
+      <c r="N110" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>TSO2500164</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>4500576103</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SP8875/BC120</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>USA-MD</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>45922</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>P8875-L01-T1204</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>70332</v>
+      </c>
+      <c r="M111" t="n">
+        <v>721429.7999999999</v>
+      </c>
+      <c r="N111" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>TSO2500169</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>4500576103</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SP8506/BC191NN</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>45912</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>P8506-L01-T1213</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>98826</v>
+      </c>
+      <c r="M112" t="n">
+        <v>721429.7999999999</v>
+      </c>
+      <c r="N112" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>TSO2500170</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>4500576228</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SP2583/HC244CM</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>USA-MD</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>P2583-L01-T1208</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>11526</v>
+      </c>
+      <c r="M113" t="n">
+        <v>336559.2</v>
+      </c>
+      <c r="N113" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>TSO2500171</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>4500576228</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SP2583/HC244CM</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>P2583-L01-T1208</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>46104</v>
+      </c>
+      <c r="M114" t="n">
+        <v>336559.2</v>
+      </c>
+      <c r="N114" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>TSO2500175</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>4500576656</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SP8316/047BW</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1596</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>45885</v>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>P8316-L03-T1202</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>10903.872</v>
+      </c>
+      <c r="M115" t="n">
+        <v>200228.3712</v>
+      </c>
+      <c r="N115" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>TSO2500176</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>4500576656</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>SP8316/247BW</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>3996</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>45878</v>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>P8316-L01-T1203</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>27428.544</v>
+      </c>
+      <c r="M116" t="n">
+        <v>200228.3712</v>
+      </c>
+      <c r="N116" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>TSO2500177</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>4500576656</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SP8316/247BW</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>3996</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>45895</v>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>P8316-L01-T1203</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>27428.544</v>
+      </c>
+      <c r="M117" t="n">
+        <v>200228.3712</v>
+      </c>
+      <c r="N117" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>TSO2500178</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>4500576656</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SP8316/247BW</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>3996</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>45902</v>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>P8316-L01-T1203</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>27428.544</v>
+      </c>
+      <c r="M118" t="n">
+        <v>200228.3712</v>
+      </c>
+      <c r="N118" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>TSO2500179</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>4500576656</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>SP8316/247BW</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>3996</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>45909</v>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>P8316-L01-T1203</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>27428.544</v>
+      </c>
+      <c r="M119" t="n">
+        <v>200228.3712</v>
+      </c>
+      <c r="N119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>TSO2500180</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>4500576656</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>SP8316/247BW</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>3996</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>45916</v>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>P8316-L01-T1203</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>27428.544</v>
+      </c>
+      <c r="M120" t="n">
+        <v>200228.3712</v>
+      </c>
+      <c r="N120" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>TSO2500181</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>4500576656</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SP8316/247W</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>3204</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>45891</v>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>P8316-L01-T1204</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>21992.256</v>
+      </c>
+      <c r="M121" t="n">
+        <v>200228.3712</v>
+      </c>
+      <c r="N121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>TSO2500182</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>4500576656</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SP8660/134W</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>996</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>45885</v>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>P8660-L03-T1202</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>11100.42</v>
+      </c>
+      <c r="M122" t="n">
+        <v>200228.3712</v>
+      </c>
+      <c r="N122" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>TSO2500183</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>4500576656</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SP8371/152B</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>45888</v>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>P8371-L01-T1202</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>17448.828</v>
+      </c>
+      <c r="M123" t="n">
+        <v>200228.3712</v>
+      </c>
+      <c r="N123" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
           <t>TSO2500184</t>
         </is>
       </c>
-      <c r="B86" t="n">
+      <c r="B124" t="n">
         <v>4500576656</v>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C124" t="inlineStr">
         <is>
           <t>SP8271/169BIW</t>
         </is>
       </c>
-      <c r="D86" t="n">
+      <c r="D124" t="n">
         <v>3996</v>
       </c>
-      <c r="E86" t="inlineStr">
+      <c r="E124" t="inlineStr">
         <is>
           <t>8月</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>柬埔寨</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>USA-GL</t>
         </is>
       </c>
-      <c r="H86" s="2" t="n">
+      <c r="H124" s="2" t="n">
         <v>45888</v>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I124" t="inlineStr">
         <is>
           <t>P8271-L01-T1205</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>不缺料</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>可立即投产</t>
-        </is>
-      </c>
-      <c r="L86" t="n">
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
         <v>38365.596</v>
       </c>
-      <c r="M86" t="n">
+      <c r="M124" t="n">
         <v>200228.3712</v>
       </c>
-      <c r="N86" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O86" t="inlineStr">
+      <c r="N124" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>TSO2500185</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>4500576656</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>SP8271/169BIW</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>8月</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>45898</v>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>P8271-L01-T1205</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>57606</v>
+      </c>
+      <c r="M125" t="n">
+        <v>200228.3712</v>
+      </c>
+      <c r="N125" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>TSO2500190</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>204103</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>SP8251/BP6685N</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>P8251-L01-T1205</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>45756</v>
+      </c>
+      <c r="M126" t="n">
+        <v>334018.8</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>TSO2500201</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>4500577403</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>SP8289/121L</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>P8289-L02-T1215</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>31146</v>
+      </c>
+      <c r="M127" t="n">
+        <v>988587.9</v>
+      </c>
+      <c r="N127" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>TSO2500203</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>4500577403</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>SP8381/209BCX</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>USA-MD</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>45920</v>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>P8381-L01-T1205</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>58506</v>
+      </c>
+      <c r="M128" t="n">
+        <v>988587.9</v>
+      </c>
+      <c r="N128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>TSO2500204</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>4500577403</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>SP8381/209BCX</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>6000</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>USA-MD</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>45927</v>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>P8381-L01-T1205</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>58506</v>
+      </c>
+      <c r="M129" t="n">
+        <v>988587.9</v>
+      </c>
+      <c r="N129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>TSO2500206</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>4500577403</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>SP8381/209TPN</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>USA-MD</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>45920</v>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>P8381-L01-T1206</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>73500</v>
+      </c>
+      <c r="M130" t="n">
+        <v>988587.9</v>
+      </c>
+      <c r="N130" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>TSO2500207</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>4500577403</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>SP8381/209TPN</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>45927</v>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>P8381-L01-T1206</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>73500</v>
+      </c>
+      <c r="M131" t="n">
+        <v>988587.9</v>
+      </c>
+      <c r="N131" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>TSO2500209</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>4500577403</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>SP8285/263SR</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>2500</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>USA-MD</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>P8285-L01-T1210</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>21745</v>
+      </c>
+      <c r="M132" t="n">
+        <v>988587.9</v>
+      </c>
+      <c r="N132" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>TSO2500210</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>4500577403</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>SP8006/565L</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>7000</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>45927</v>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>P8006-L01-T1209</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>55860</v>
+      </c>
+      <c r="M133" t="n">
+        <v>988587.9</v>
+      </c>
+      <c r="N133" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>TSO2500214</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>4500577403</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SP8390/753</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>45927</v>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>P8390-L01-T1201</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>37629</v>
+      </c>
+      <c r="M134" t="n">
+        <v>988587.9</v>
+      </c>
+      <c r="N134" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>TSO2500215</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>4500577403</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>SP8012/888</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>9000</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>45920</v>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>P8012-L01-T1201</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>135423</v>
+      </c>
+      <c r="M135" t="n">
+        <v>988587.9</v>
+      </c>
+      <c r="N135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>完整</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>TSO2500216</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>4500577403</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SP8392/910L</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>9月</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>柬埔寨</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>USA-GL</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>45925</v>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>P8392-L03-T1214</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>不缺料</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>可立即投产</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>70000</v>
+      </c>
+      <c r="M136" t="n">
+        <v>988587.9</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O136" t="inlineStr">
         <is>
           <t>完整</t>
         </is>
@@ -6100,16 +9350,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D2" t="n">
-        <v>44424</v>
+        <v>71098</v>
       </c>
       <c r="E2" t="n">
-        <v>418716.108</v>
+        <v>640405.71</v>
       </c>
       <c r="F2" t="n">
-        <v>3115303.2948</v>
+        <v>5218217.2148</v>
       </c>
     </row>
     <row r="3">
@@ -6124,16 +9374,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D3" t="n">
-        <v>73354</v>
+        <v>125950</v>
       </c>
       <c r="E3" t="n">
-        <v>841591.884</v>
+        <v>1489820.128</v>
       </c>
       <c r="F3" t="n">
-        <v>5094422.1212</v>
+        <v>9993463.626</v>
       </c>
     </row>
     <row r="4">
@@ -6148,16 +9398,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="D4" t="n">
-        <v>143052</v>
+        <v>184290</v>
       </c>
       <c r="E4" t="n">
-        <v>1605033.661</v>
+        <v>2031491.173</v>
       </c>
       <c r="F4" t="n">
-        <v>9679646.678099999</v>
+        <v>12604502.7257</v>
       </c>
     </row>
     <row r="5">
@@ -6172,16 +9422,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>23000</v>
+        <v>131488</v>
       </c>
       <c r="E5" t="n">
-        <v>198574</v>
+        <v>1488702.632</v>
       </c>
       <c r="F5" t="n">
-        <v>1783709.74</v>
+        <v>16938295.3536</v>
       </c>
     </row>
   </sheetData>
@@ -6217,7 +9467,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>85</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3">
@@ -6227,7 +9477,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>283830</v>
+        <v>512826</v>
       </c>
     </row>
     <row r="4">
@@ -6238,7 +9488,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>$3,063,915.65</t>
+          <t>$5,650,419.64</t>
         </is>
       </c>
     </row>
@@ -6250,7 +9500,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>¥19,673,081.83</t>
+          <t>¥44,754,478.92</t>
         </is>
       </c>
     </row>
@@ -6261,7 +9511,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7">
@@ -6271,7 +9521,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
@@ -6281,7 +9531,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>64</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9">
@@ -6291,7 +9541,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
